--- a/data/trending_integrated_20261022_11.xlsx
+++ b/data/trending_integrated_20261022_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3690</v>
+        <v>3665</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.42%</t>
+          <t>'+18.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>51522248498</v>
+        <v>54482649221</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설에 따른 급등 가능성 언급. 전쟁 가능성 관련 추측성 내용.</t>
+          <t>김정은 신변 이상설 및 사망설 관련 급등 가능성 분석. 전쟁 가능성 대두 및 단기 급등 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '신변 이상설', '전쟁 가능성']</t>
+          <t>['김정은', '신변이상설', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>유니켐</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7850</v>
+        <v>55600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.87%</t>
+          <t>'+16.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>243</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>998</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6660</v>
+        <v>47700</v>
       </c>
       <c r="K3" t="n">
-        <v>6710</v>
+        <v>51000</v>
       </c>
       <c r="L3" t="n">
-        <v>8430</v>
+        <v>56500</v>
       </c>
       <c r="M3" t="n">
-        <v>6640</v>
+        <v>50500</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>6985290450</v>
+        <v>460653688700</v>
       </c>
       <c r="P3" t="n">
-        <v>8430</v>
+        <v>67300</v>
       </c>
       <c r="Q3" t="n">
-        <v>391</v>
+        <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>38000</v>
+        <v>1412000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 기업 루미아 인수 관련 기대감 상승. 휴머노이드 로봇 사업 확장 전망 및 50배 상승 가능성 언급.</t>
+          <t>실적 발표 어닝 서프라이즈, 주식 소각 결정, 전망 상향, 자사주 취득 등 긍정적 공시 다수 확인.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['루미아 인수', '휴머노이드 로봇', '사업 확장']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>011330</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>유니켐</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55500</v>
+        <v>7630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.35%</t>
+          <t>'+14.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>954</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
-        <v>37.72</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>47700</v>
+        <v>6660</v>
       </c>
       <c r="K4" t="n">
-        <v>51000</v>
+        <v>6710</v>
       </c>
       <c r="L4" t="n">
-        <v>56500</v>
+        <v>8430</v>
       </c>
       <c r="M4" t="n">
-        <v>50500</v>
+        <v>6640</v>
       </c>
       <c r="N4" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>453125211250</v>
+        <v>7270792300</v>
       </c>
       <c r="P4" t="n">
-        <v>67300</v>
+        <v>8430</v>
       </c>
       <c r="Q4" t="n">
-        <v>23150</v>
+        <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>1412000</v>
+        <v>38000</v>
       </c>
       <c r="S4" t="n">
-        <v>410000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>실적 발표 어닝 서프라이즈, 주식 소각 결정, 전망 상향, 자사주 취득 등 긍정적 공시 다수 확인.</t>
+          <t>미국 기업 루미아 인수 관련 기대감 상승. 휴머노이드 로봇 사업 확장 전망 및 50배 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
+          <t>['루미아 인수', '휴머노이드 로봇', '사업 확장']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>011330</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18600</v>
+        <v>1662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+3.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.32</v>
+        <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H5" t="n">
-        <v>3.29</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17920</v>
+        <v>1610</v>
       </c>
       <c r="K5" t="n">
-        <v>19180</v>
+        <v>1655</v>
       </c>
       <c r="L5" t="n">
-        <v>20150</v>
+        <v>1780</v>
       </c>
       <c r="M5" t="n">
-        <v>18370</v>
+        <v>1622</v>
       </c>
       <c r="N5" t="n">
-        <v>3.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>62828422940</v>
+        <v>9573782490</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>3980</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>1115</v>
       </c>
       <c r="R5" t="n">
-        <v>-2000</v>
+        <v>126000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 보안주 초급등 및 보안 이슈 확산에 따른 라온시큐어 주목. AI 발전과 함께 보안 산업 성장 전망.</t>
+          <t>매각 관련 불확실성 속 주가조작 및 하한가에 대한 언급. 향후 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안', 'AI', 'PHP']</t>
+          <t>['매각', '주가조작', '공시']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1667</v>
+        <v>18455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.39</v>
+        <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>3.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1610</v>
+        <v>17920</v>
       </c>
       <c r="K6" t="n">
-        <v>1655</v>
+        <v>19180</v>
       </c>
       <c r="L6" t="n">
-        <v>1780</v>
+        <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>1622</v>
+        <v>18370</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>9452637011</v>
+        <v>63790769780</v>
       </c>
       <c r="P6" t="n">
-        <v>3980</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>1115</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>126000</v>
+        <v>-2000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>매각 관련 불확실성 속 주가조작 및 하한가에 대한 언급. 향후 주가 상승 기대.</t>
+          <t>미국 보안주 초급등 및 보안 이슈 확산에 따른 라온시큐어 주목. AI 발전과 함께 보안 산업 성장 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['매각', '주가조작', '공시']</t>
+          <t>['보안', 'AI', 'PHP']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14390</v>
+        <v>14260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.33</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
         <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="H7" t="n">
         <v>3.48</v>
@@ -1070,7 +1070,7 @@
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>77046618570</v>
+        <v>79118679125</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 광통신 관련 뉴스 및 기술 개발(EUV용 유리기판) 언급. 기관 매집 정황 포착.</t>
+          <t>엔비디아 AI 광통신 관련 뉴스 기반 기대감. EUV용 유리기판 제조 기술 확보 및 기관 매집 신호.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 광통신', 'EUV', '기관 매집']</t>
+          <t>['AI', '광통신', '유리기판']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14790</v>
+        <v>14700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.14%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="H8" t="n">
         <v>9.949999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>15290</v>
       </c>
       <c r="M8" t="n">
-        <v>14700</v>
+        <v>14680</v>
       </c>
       <c r="N8" t="n">
         <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>28052050100</v>
+        <v>29020737845</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41750</v>
+        <v>41850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>7070398875</v>
+        <v>7688318850</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7210</v>
+        <v>7200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="H10" t="n">
         <v>25.47</v>
@@ -1346,7 +1346,7 @@
         <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>6786652985</v>
+        <v>7238957085</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>217750</v>
+        <v>217250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.57%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G11" t="n">
-        <v>1353</v>
+        <v>1327</v>
       </c>
       <c r="H11" t="n">
         <v>46.14</v>
@@ -1432,13 +1432,13 @@
         <v>226000</v>
       </c>
       <c r="M11" t="n">
-        <v>217000</v>
+        <v>216000</v>
       </c>
       <c r="N11" t="n">
         <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>976905899000</v>
+        <v>1034947446000</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주요 내용이 정치적 언급으로 채워져 있으며, 주가 관련 구체적 근거 제시 부족.</t>
+          <t>정치적 언급과 함께 증시 하락 전망 및 삼성전자 하락 요인 분석. 외인 놀이터화 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '외인 놀이터']</t>
+          <t>['한국증시', '정치', '전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9900</v>
+        <v>9870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-3.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F12" t="n">
         <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H12" t="n">
         <v>5.87</v>
@@ -1530,7 +1530,7 @@
         <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>11536081850</v>
+        <v>11661404995</v>
       </c>
       <c r="P12" t="n">
         <v>14940</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>테슬라 실적 관련 언급 있으나, 주가 하락 및 공매도 관련 부정적 언급 다수. 명확한 근거 제시 미흡.</t>
+          <t>테슬라 실적 상회 및 스페이스X 상장 이슈 기반의 기대감. 다만, 개인 물량 털기 및 공매도 우려 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도']</t>
+          <t>['테슬라', '실적', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,184 +1575,184 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14550</v>
+        <v>1252000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>487</v>
       </c>
       <c r="G13" t="n">
-        <v>102</v>
+        <v>1613</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>48.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>1294000</v>
       </c>
       <c r="K13" t="n">
-        <v>14460</v>
+        <v>1273000</v>
       </c>
       <c r="L13" t="n">
-        <v>16140</v>
+        <v>1297000</v>
       </c>
       <c r="M13" t="n">
-        <v>13550</v>
+        <v>1246000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>67604887880</v>
+        <v>1231724438500</v>
       </c>
       <c r="P13" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>12030</v>
+        <v>468000</v>
       </c>
       <c r="R13" t="n">
-        <v>-54000</v>
+        <v>-55000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
+          <t>정치적 이슈와 연계된 SK하이닉스 하락 관련 언급. 솔리다임 상장 이슈 및 외인 매도 증가 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수주잔고']</t>
+          <t>['반도체', '정치', '외인매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1255000</v>
+        <v>14290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.01%</t>
+          <t>'-4.61%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
-        <v>497</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>1591</v>
+        <v>108</v>
       </c>
       <c r="H14" t="n">
-        <v>48.79</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1294000</v>
+        <v>14980</v>
       </c>
       <c r="K14" t="n">
-        <v>1273000</v>
+        <v>14460</v>
       </c>
       <c r="L14" t="n">
-        <v>1297000</v>
+        <v>16140</v>
       </c>
       <c r="M14" t="n">
-        <v>1248000</v>
+        <v>13550</v>
       </c>
       <c r="N14" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1182487500500</v>
+        <v>68735839490</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q14" t="n">
-        <v>468000</v>
+        <v>12030</v>
       </c>
       <c r="R14" t="n">
-        <v>-55000</v>
+        <v>-54000</v>
       </c>
       <c r="S14" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 외인 매도 증가, 솔리다임 상장 철회 이슈 언급. 주가 상승 근거 부족.</t>
+          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['솔리다임', '외인 매도']</t>
+          <t>['AI', '반도체', '수주잔고']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10220</v>
+        <v>10040</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.26%</t>
+          <t>'-9.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1800,13 +1800,13 @@
         <v>10880</v>
       </c>
       <c r="M15" t="n">
-        <v>10050</v>
+        <v>9930</v>
       </c>
       <c r="N15" t="n">
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>43812881360</v>
+        <v>46801139885</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 관련 언급 후 투자경고, 투기예고 등 하락 요인 언급. ESS 마진율 불확실성 지적.</t>
+          <t>로봇주 NXT 시장 폭등과 관련한 언급. 투자경고 및 투기 과열 우려, ESS 마진율 불확실성 기반 하락 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투자경고', 'ESS']</t>
+          <t>['로봇주', '투자경고', '하락']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_11.xlsx
+++ b/data/trending_integrated_20261022_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3665</v>
+        <v>3695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.61%</t>
+          <t>'+19.58%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>54482649221</v>
+        <v>56217317653</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55600</v>
+        <v>55500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.56%</t>
+          <t>'+16.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F3" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>998</v>
+        <v>1033</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>460653688700</v>
+        <v>468428211950</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7630</v>
+        <v>7620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.56%</t>
+          <t>'+14.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>7270792300</v>
+        <v>7409298885</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1662</v>
+        <v>1671</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.23%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>9573782490</v>
+        <v>9691957941</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18455</v>
+        <v>18360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -972,13 +972,13 @@
         <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>18370</v>
+        <v>18280</v>
       </c>
       <c r="N6" t="n">
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>63790769780</v>
+        <v>64789669080</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14260</v>
+        <v>14700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>366</v>
+        <v>188</v>
       </c>
       <c r="H7" t="n">
-        <v>3.48</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14310</v>
+        <v>14770</v>
       </c>
       <c r="K7" t="n">
-        <v>14180</v>
+        <v>14770</v>
       </c>
       <c r="L7" t="n">
-        <v>14830</v>
+        <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>13890</v>
+        <v>14610</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>79118679125</v>
+        <v>29885859840</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>1640</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-389000</v>
+        <v>-69000</v>
       </c>
       <c r="S7" t="n">
-        <v>16000</v>
+        <v>-22000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>엔비디아 AI 광통신 관련 뉴스 기반 기대감. EUV용 유리기판 제조 기술 확보 및 기관 매집 신호.</t>
+          <t>대우건설 주가 부진 및 건설주 전반의 상승 모멘텀 부족. 외국인 및 연기금 매수세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '유리기판']</t>
+          <t>['건설주', '외국인', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,99 +1108,99 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14700</v>
+        <v>14110</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>182</v>
+        <v>370</v>
       </c>
       <c r="H8" t="n">
-        <v>9.949999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14770</v>
+        <v>14310</v>
       </c>
       <c r="K8" t="n">
-        <v>14770</v>
+        <v>14180</v>
       </c>
       <c r="L8" t="n">
-        <v>15290</v>
+        <v>14830</v>
       </c>
       <c r="M8" t="n">
-        <v>14680</v>
+        <v>13890</v>
       </c>
       <c r="N8" t="n">
-        <v>9.82</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>29020737845</v>
+        <v>80980442080</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R8" t="n">
-        <v>-69000</v>
+        <v>-389000</v>
       </c>
       <c r="S8" t="n">
-        <v>-22000</v>
+        <v>16000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>타 건설주 대비 낮은 상승률 및 경영 방식 비판, 정치적 언급과 함께 대차해지 운동 촉구.</t>
+          <t>AI 광통신 관련 뉴스 및 기술 확보 소식에 따른 대한광통신 주가 상승 기대감. 기관 매집 신호.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['건설주', '경영 방식', '대차해지']</t>
+          <t>['AI', '광통신', '기술']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41850</v>
+        <v>41650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="n">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>7688318850</v>
+        <v>7951870600</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7200</v>
+        <v>7180</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-2.31%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="H10" t="n">
         <v>25.47</v>
@@ -1340,19 +1340,19 @@
         <v>7340</v>
       </c>
       <c r="M10" t="n">
-        <v>7190</v>
+        <v>7170</v>
       </c>
       <c r="N10" t="n">
         <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>7238957085</v>
+        <v>7773952310</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>7190</v>
+        <v>7170</v>
       </c>
       <c r="R10" t="n">
         <v>-180000</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>217250</v>
+        <v>9840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.80%</t>
+          <t>'-3.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>465</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
-        <v>1327</v>
+        <v>286</v>
       </c>
       <c r="H11" t="n">
-        <v>46.14</v>
+        <v>5.87</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>223500</v>
+        <v>10190</v>
       </c>
       <c r="K11" t="n">
-        <v>221500</v>
+        <v>10110</v>
       </c>
       <c r="L11" t="n">
-        <v>226000</v>
+        <v>10180</v>
       </c>
       <c r="M11" t="n">
-        <v>216000</v>
+        <v>9720</v>
       </c>
       <c r="N11" t="n">
-        <v>46.08</v>
+        <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>1034947446000</v>
+        <v>12044548635</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>14940</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>5390</v>
       </c>
       <c r="R11" t="n">
-        <v>-677000</v>
+        <v>-32000</v>
       </c>
       <c r="S11" t="n">
-        <v>-254000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 증시 하락 전망 및 삼성전자 하락 요인 분석. 외인 놀이터화 우려.</t>
+          <t>테슬라 실적 발표 후 명신산업 주가 하락세. 공매도 추정 및 개미 털기 구간 분석.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['한국증시', '정치', '전망']</t>
+          <t>['테슬라', '실적', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9870</v>
+        <v>215750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.14%</t>
+          <t>'-3.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>464</v>
       </c>
       <c r="G12" t="n">
-        <v>282</v>
+        <v>1254</v>
       </c>
       <c r="H12" t="n">
-        <v>5.87</v>
+        <v>46.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10190</v>
+        <v>223500</v>
       </c>
       <c r="K12" t="n">
-        <v>10110</v>
+        <v>221500</v>
       </c>
       <c r="L12" t="n">
-        <v>10180</v>
+        <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>9720</v>
+        <v>215500</v>
       </c>
       <c r="N12" t="n">
-        <v>5.34</v>
+        <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>11661404995</v>
+        <v>1073196794250</v>
       </c>
       <c r="P12" t="n">
-        <v>14940</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>5390</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-32000</v>
+        <v>-677000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-254000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 상장 이슈 기반의 기대감. 다만, 개인 물량 털기 및 공매도 우려 존재.</t>
+          <t>정치적 이슈로 인한 한국 증시 하락 전망 및 삼성전자 주가 하락 우려. 외인 매수세 지속.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테슬라', '실적', '공매도']</t>
+          <t>['한국증시', '전망', '외인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1252000</v>
+        <v>1245000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-3.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="G13" t="n">
-        <v>1613</v>
+        <v>1665</v>
       </c>
       <c r="H13" t="n">
         <v>48.79</v>
@@ -1616,13 +1616,13 @@
         <v>1297000</v>
       </c>
       <c r="M13" t="n">
-        <v>1246000</v>
+        <v>1244000</v>
       </c>
       <c r="N13" t="n">
         <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>1231724438500</v>
+        <v>1267729177500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 SK하이닉스 하락 관련 언급. 솔리다임 상장 이슈 및 외인 매도 증가 우려.</t>
+          <t>정치적 이슈 및 솔리다임 상장 이슈로 인한 SK하이닉스 주가 하락 및 반도체 산업 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '정치', '외인매도']</t>
+          <t>['반도체', '정치', '상장']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14290</v>
+        <v>14260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.61%</t>
+          <t>'-4.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H14" t="n">
         <v>1.2</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>68735839490</v>
+        <v>69726599915</v>
       </c>
       <c r="P14" t="n">
         <v>28800</v>
@@ -1774,13 +1774,13 @@
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1800,13 +1800,13 @@
         <v>10880</v>
       </c>
       <c r="M15" t="n">
-        <v>9930</v>
+        <v>9920</v>
       </c>
       <c r="N15" t="n">
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>46801139885</v>
+        <v>48852585200</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 NXT 시장 폭등과 관련한 언급. 투자경고 및 투기 과열 우려, ESS 마진율 불확실성 기반 하락 전망.</t>
+          <t>로봇주 NXT 급등 후 HT로보틱스 주가 급락. 투자경고 및 투기 과열 종목 지정에 따른 하락세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투자경고', '하락']</t>
+          <t>['로봇주', '투자경고', '급락']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_11.xlsx
+++ b/data/trending_integrated_20261022_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3695</v>
+        <v>3645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.58%</t>
+          <t>'+17.96%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>56217317653</v>
+        <v>57820403763</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설 및 사망설 관련 급등 가능성 분석. 전쟁 가능성 대두 및 단기 급등 기대.</t>
+          <t>김정은 신변 이상설 및 사망설로 인한 급등세. 전쟁 가능성 대두 및 관련 뉴스로 인한 변동성 확대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '신변이상설', '급등']</t>
+          <t>['김정은', '신변 이상설', '전쟁 가능성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55500</v>
+        <v>55600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.35%</t>
+          <t>'+16.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G3" t="n">
-        <v>1033</v>
+        <v>1073</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>468428211950</v>
+        <v>475077942900</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>실적 발표 어닝 서프라이즈, 주식 소각 결정, 전망 상향, 자사주 취득 등 긍정적 공시 다수 확인.</t>
+          <t>삼성E&amp;A, 슈퍼 울트라 최강 어닝 서프라이즈 기록. 주식 소각 결정 및 전망 상향 공시, 영업실적 수정 발표. MSCI 11월 편입 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
+          <t>['어닝 서프라이즈', '주식 소각', 'MSCI 편입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7620</v>
+        <v>7630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.41%</t>
+          <t>'+14.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>7409298885</v>
+        <v>7463796645</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 기업 루미아 인수 관련 기대감 상승. 휴머노이드 로봇 사업 확장 전망 및 50배 상승 가능성 언급.</t>
+          <t>유니켐, 미국 기업 루미아 인수 및 로봇공학 센싱 솔루션 양산 기대감. 50배 상승 가능성 및 점상한가 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아 인수', '휴머노이드 로봇', '사업 확장']</t>
+          <t>['루미아 인수', '로봇공학', '센싱 솔루션']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+3.54%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
         <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>9691957941</v>
+        <v>9838834628</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18360</v>
+        <v>18390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -978,7 +978,7 @@
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>64789669080</v>
+        <v>65352281585</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14700</v>
+        <v>14755</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
         <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>29885859840</v>
+        <v>30375241760</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14110</v>
+        <v>14170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.40%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.33</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="H8" t="n">
         <v>3.48</v>
@@ -1162,7 +1162,7 @@
         <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>80980442080</v>
+        <v>82321062875</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 광통신 관련 뉴스 및 기술 확보 소식에 따른 대한광통신 주가 상승 기대감. 기관 매집 신호.</t>
+          <t>엔비디아 AI 광통신 관련 기술 확보 및 EUV용 유리기판 제조 기술 발표. 기관 매집 시작 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '기술']</t>
+          <t>['AI 광통신', 'EUV 유리기판', '기관 매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41650</v>
+        <v>41800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.65%</t>
+          <t>'-1.30%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>7951870600</v>
+        <v>8314885350</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 언급되나, C1/C2 확률 및 승인 근거에 대한 불확실성 혼재. 공매도 관련 언급.</t>
+          <t>HLB, 간암 치료제 FDA 승인에 대한 기대와 우려 공존. 기관 매수세 확인, 1주일 내 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암', '공매도']</t>
+          <t>['간암 치료제', 'FDA 승인', '기관 수급']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7180</v>
+        <v>7190</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.31%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H10" t="n">
         <v>25.47</v>
@@ -1346,7 +1346,7 @@
         <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>7773952310</v>
+        <v>8340724230</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>지속적인 적자와 낮은 주가 수준에 대한 불만. 실적 부진에도 불구하고 바닥권이라는 인식과 함께 단기 반등 가능성 언급. OLED 관련 뉴스 혼재.</t>
+          <t>LG디스플레이, 심각한 적자와 낮은 주가에 대한 불만 토로. 10년 이상 투자에도 성과 부진, 신저가 수준.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적 부진', '바닥권', 'OLED']</t>
+          <t>['적자', '주가 부진', '신저가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9840</v>
+        <v>216000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.43%</t>
+          <t>'-3.36%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>470</v>
       </c>
       <c r="G11" t="n">
-        <v>286</v>
+        <v>1252</v>
       </c>
       <c r="H11" t="n">
-        <v>5.87</v>
+        <v>46.14</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10190</v>
+        <v>223500</v>
       </c>
       <c r="K11" t="n">
-        <v>10110</v>
+        <v>221500</v>
       </c>
       <c r="L11" t="n">
-        <v>10180</v>
+        <v>226000</v>
       </c>
       <c r="M11" t="n">
-        <v>9720</v>
+        <v>215000</v>
       </c>
       <c r="N11" t="n">
-        <v>5.34</v>
+        <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>12044548635</v>
+        <v>1104599149000</v>
       </c>
       <c r="P11" t="n">
-        <v>14940</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>5390</v>
+        <v>94500</v>
       </c>
       <c r="R11" t="n">
-        <v>-32000</v>
+        <v>-677000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-254000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>테슬라 실적 발표 후 명신산업 주가 하락세. 공매도 추정 및 개미 털기 구간 분석.</t>
+          <t>국내 증시 전반에 대한 부정적 전망과 특정 정치 세력에 대한 비판이 주를 이룸. 외인 투자자 놀이터화 우려 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '실적', '공매도']</t>
+          <t>['한국 증시', '정치 테마', '외인 투자']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>215750</v>
+        <v>1248000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="G12" t="n">
-        <v>1254</v>
+        <v>1793</v>
       </c>
       <c r="H12" t="n">
-        <v>46.14</v>
+        <v>48.79</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>223500</v>
+        <v>1294000</v>
       </c>
       <c r="K12" t="n">
-        <v>221500</v>
+        <v>1273000</v>
       </c>
       <c r="L12" t="n">
-        <v>226000</v>
+        <v>1297000</v>
       </c>
       <c r="M12" t="n">
-        <v>215500</v>
+        <v>1243000</v>
       </c>
       <c r="N12" t="n">
-        <v>46.08</v>
+        <v>48.77</v>
       </c>
       <c r="O12" t="n">
-        <v>1073196794250</v>
+        <v>1306731734500</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R12" t="n">
-        <v>-677000</v>
+        <v>-55000</v>
       </c>
       <c r="S12" t="n">
-        <v>-254000</v>
+        <v>-6000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 한국 증시 하락 전망 및 삼성전자 주가 하락 우려. 외인 매수세 지속.</t>
+          <t>정치적 이슈와 특정 세력에 대한 비판이 주된 내용. 반도체 산업 전망에 대한 부정적 시각과 함께 외인 매도 증가.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['한국증시', '전망', '외인']</t>
+          <t>['정치 테마', '반도체 산업', '외인 매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,178 +1568,178 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1245000</v>
+        <v>14400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.79%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>477</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>1665</v>
+        <v>131</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>14980</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>14460</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>16140</v>
       </c>
       <c r="M13" t="n">
-        <v>1244000</v>
+        <v>13550</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1267729177500</v>
+        <v>70368136315</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>12030</v>
       </c>
       <c r="R13" t="n">
-        <v>-55000</v>
+        <v>-54000</v>
       </c>
       <c r="S13" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 솔리다임 상장 이슈로 인한 SK하이닉스 주가 하락 및 반도체 산업 우려.</t>
+          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '정치', '상장']</t>
+          <t>['AI', '반도체', '수주잔고']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14260</v>
+        <v>9780</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.81%</t>
+          <t>'-4.02%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>118</v>
+        <v>295</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2</v>
+        <v>5.87</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14980</v>
+        <v>10190</v>
       </c>
       <c r="K14" t="n">
-        <v>14460</v>
+        <v>10110</v>
       </c>
       <c r="L14" t="n">
-        <v>16140</v>
+        <v>10180</v>
       </c>
       <c r="M14" t="n">
-        <v>13550</v>
+        <v>9720</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="O14" t="n">
-        <v>69726599915</v>
+        <v>12352514055</v>
       </c>
       <c r="P14" t="n">
-        <v>28800</v>
+        <v>14940</v>
       </c>
       <c r="Q14" t="n">
-        <v>12030</v>
+        <v>5390</v>
       </c>
       <c r="R14" t="n">
-        <v>-54000</v>
+        <v>-32000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
+          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스가 있으나, 주가 하락 및 대량 매도에 대한 우려와 불만이 공존.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수주잔고']</t>
+          <t>['테슬라', '스페이스X', '매도세']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10040</v>
+        <v>10170</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.87%</t>
+          <t>'-8.71%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>48852585200</v>
+        <v>50301587740</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 NXT 급등 후 HT로보틱스 주가 급락. 투자경고 및 투기 과열 종목 지정에 따른 하락세.</t>
+          <t>로봇주 HT로보틱스, 투자경고 및 투매 예고로 인한 급락세. ESS 마진율 불확실성 및 복구 어려운 하락 파동 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261022_11.xlsx
+++ b/data/trending_integrated_20261022_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3645</v>
+        <v>3655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.96%</t>
+          <t>'+18.28%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>57820403763</v>
+        <v>58581983809</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설 및 사망설로 인한 급등세. 전쟁 가능성 대두 및 관련 뉴스로 인한 변동성 확대.</t>
+          <t>김정은 신변 이상설 및 전쟁 가능성 대두에 따른 급등. 단기적 테마주로서의 움직임.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '신변 이상설', '전쟁 가능성']</t>
+          <t>['김정은 신변 이상설', '전쟁 가능성', '테마주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F3" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G3" t="n">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>475077942900</v>
+        <v>478968162300</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 슈퍼 울트라 최강 어닝 서프라이즈 기록. 주식 소각 결정 및 전망 상향 공시, 영업실적 수정 발표. MSCI 11월 편입 예상.</t>
+          <t>실적 발표 어닝 서프라이즈 및 주식 소각 결정, 자사주 취득, 전망 상향 등 다수의 긍정적 공시 확인. MSCI 편입 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7630</v>
+        <v>7570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.56%</t>
+          <t>'+13.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>7463796645</v>
+        <v>7776545780</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유니켐, 미국 기업 루미아 인수 및 로봇공학 센싱 솔루션 양산 기대감. 50배 상승 가능성 및 점상한가 전망.</t>
+          <t>미국 기업 루미아 인수 및 촉각 센서 기술 개발 관련 다수의 긍정적 뉴스 확인. 향후 큰 폭의 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아 인수', '로봇공학', '센싱 솔루션']</t>
+          <t>['촉각 센서', '루미아 인수', '로봇 공학']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1667</v>
+        <v>1744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+8.32%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -877,7 +877,7 @@
         <v>1655</v>
       </c>
       <c r="L5" t="n">
-        <v>1780</v>
+        <v>1825</v>
       </c>
       <c r="M5" t="n">
         <v>1622</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>9838834628</v>
+        <v>13114499395</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18390</v>
+        <v>18360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -978,7 +978,7 @@
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>65352281585</v>
+        <v>65757038425</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14755</v>
+        <v>14730</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.10%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>30375241760</v>
+        <v>30839374525</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설 주가 부진 및 건설주 전반의 상승 모멘텀 부족. 외국인 및 연기금 매수세.</t>
+          <t>건설주 전반의 상승 속에서 상대적 약세 언급. 정치 관련 언급 및 대차해지 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['건설주', '외국인', '실적']</t>
+          <t>['건설주', '주가 부양', '대차해지']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14170</v>
+        <v>14180</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'-0.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.33</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H8" t="n">
         <v>3.48</v>
@@ -1162,7 +1162,7 @@
         <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>82321062875</v>
+        <v>83082779680</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41800</v>
+        <v>41600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.30%</t>
+          <t>'-1.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F9" t="n">
         <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>8314885350</v>
+        <v>8457707350</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB, 간암 치료제 FDA 승인에 대한 기대와 우려 공존. 기관 매수세 확인, 1주일 내 급등 가능성 언급.</t>
+          <t>간암 치료제 FDA 승인 관련 기대감과 불확실성 혼재. 기관 수급은 긍정적이나 결과에 따른 변동성 예상.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="H10" t="n">
         <v>25.47</v>
@@ -1346,7 +1346,7 @@
         <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>8340724230</v>
+        <v>8577319815</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LG디스플레이, 심각한 적자와 낮은 주가에 대한 불만 토로. 10년 이상 투자에도 성과 부진, 신저가 수준.</t>
+          <t>장기 적자 및 주가 하락세 지속, 실적 발표 후 폭락 및 최저가 수준 기록. 긍정적 전망은 희박.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['적자', '주가 부진', '신저가']</t>
+          <t>['영업손실', '주가 하락', '최저가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>216000</v>
+        <v>215750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-3.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G11" t="n">
-        <v>1252</v>
+        <v>1198</v>
       </c>
       <c r="H11" t="n">
         <v>46.14</v>
@@ -1438,7 +1438,7 @@
         <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1104599149000</v>
+        <v>1133910203500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 증시 전반에 대한 부정적 전망과 특정 정치 세력에 대한 비판이 주를 이룸. 외인 투자자 놀이터화 우려 제기.</t>
+          <t>정치적 이슈와 부정적인 증시 전망 관련 언급 다수. 외인 놀이터화 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['한국 증시', '정치 테마', '외인 투자']</t>
+          <t>['정치적 이슈', '증시 전망', '외인 투자']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1248000</v>
+        <v>14460</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-3.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>485</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>1793</v>
+        <v>128</v>
       </c>
       <c r="H12" t="n">
-        <v>48.79</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1294000</v>
+        <v>14980</v>
       </c>
       <c r="K12" t="n">
-        <v>1273000</v>
+        <v>14460</v>
       </c>
       <c r="L12" t="n">
-        <v>1297000</v>
+        <v>16140</v>
       </c>
       <c r="M12" t="n">
-        <v>1243000</v>
+        <v>13550</v>
       </c>
       <c r="N12" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1306731734500</v>
+        <v>70921578220</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q12" t="n">
-        <v>468000</v>
+        <v>12030</v>
       </c>
       <c r="R12" t="n">
-        <v>-55000</v>
+        <v>-54000</v>
       </c>
       <c r="S12" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 특정 세력에 대한 비판이 주된 내용. 반도체 산업 전망에 대한 부정적 시각과 함께 외인 매도 증가.</t>
+          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치 테마', '반도체 산업', '외인 매도']</t>
+          <t>['AI', '반도체', '수주잔고']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14400</v>
+        <v>1242000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-4.02%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="G13" t="n">
-        <v>131</v>
+        <v>1847</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>48.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>1294000</v>
       </c>
       <c r="K13" t="n">
-        <v>14460</v>
+        <v>1273000</v>
       </c>
       <c r="L13" t="n">
-        <v>16140</v>
+        <v>1297000</v>
       </c>
       <c r="M13" t="n">
-        <v>13550</v>
+        <v>1240000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>70368136315</v>
+        <v>1339472702500</v>
       </c>
       <c r="P13" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>12030</v>
+        <v>468000</v>
       </c>
       <c r="R13" t="n">
-        <v>-54000</v>
+        <v>-55000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
+          <t>정치적 이슈와 연관된 부정적 언급이 주를 이루며 반도체 산업 침체 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수주잔고']</t>
+          <t>['정치적 이슈', '반도체 산업', '증시 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9780</v>
+        <v>9700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.02%</t>
+          <t>'-4.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.53</v>
       </c>
       <c r="E14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H14" t="n">
         <v>5.87</v>
@@ -1708,13 +1708,13 @@
         <v>10180</v>
       </c>
       <c r="M14" t="n">
-        <v>9720</v>
+        <v>9700</v>
       </c>
       <c r="N14" t="n">
         <v>5.34</v>
       </c>
       <c r="O14" t="n">
-        <v>12352514055</v>
+        <v>12851685775</v>
       </c>
       <c r="P14" t="n">
         <v>14940</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스가 있으나, 주가 하락 및 대량 매도에 대한 우려와 불만이 공존.</t>
+          <t>테슬라 실적 호조와 스페이스X 관련 뉴스에도 불구하고 주가 하락 및 공매도 관련 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '매도세']</t>
+          <t>['테슬라', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10170</v>
+        <v>10040</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.71%</t>
+          <t>'-9.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>50301587740</v>
+        <v>50917951535</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 HT로보틱스, 투자경고 및 투매 예고로 인한 급락세. ESS 마진율 불확실성 및 복구 어려운 하락 파동 우려.</t>
+          <t>로봇주 테마 속에서도 투자경고 및 투기예고로 인한 급락세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>

--- a/data/trending_integrated_20261022_11.xlsx
+++ b/data/trending_integrated_20261022_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3655</v>
+        <v>3635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.28%</t>
+          <t>'+17.64%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>58581983809</v>
+        <v>59060580328</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55600</v>
+        <v>55800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.56%</t>
+          <t>'+16.98%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F3" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G3" t="n">
-        <v>1081</v>
+        <v>1099</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>478968162300</v>
+        <v>484220554700</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>실적 발표 어닝 서프라이즈 및 주식 소각 결정, 자사주 취득, 전망 상향 등 다수의 긍정적 공시 확인. MSCI 편입 예상.</t>
+          <t>삼성E&amp;A, 어닝 서프라이즈 및 주식 소각 결정, 전망 상향 공시. MSCI 편입 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', 'MSCI 편입']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7570</v>
+        <v>7430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.66%</t>
+          <t>'+11.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>7776545780</v>
+        <v>8002329970</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1744</v>
+        <v>1771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.32%</t>
+          <t>'+10.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -877,7 +877,7 @@
         <v>1655</v>
       </c>
       <c r="L5" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="M5" t="n">
         <v>1622</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>13114499395</v>
+        <v>15858304743</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>매각 관련 불확실성 속 주가조작 및 하한가에 대한 언급. 향후 주가 상승 기대.</t>
+          <t>푸드나무, 보호예수 해제 및 인수설 속 주가 변동성 확대. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['매각', '주가조작', '공시']</t>
+          <t>['보호예수 해제', '인수설', '주가 조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18360</v>
+        <v>18410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -978,7 +978,7 @@
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>65757038425</v>
+        <v>66005075010</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14730</v>
+        <v>14830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>30839374525</v>
+        <v>31205427045</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14180</v>
+        <v>14230</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.91%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.33</v>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H8" t="n">
         <v>3.48</v>
@@ -1162,7 +1162,7 @@
         <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>83082779680</v>
+        <v>83800062810</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41600</v>
+        <v>41750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.77%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>8457707350</v>
+        <v>8655598750</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>간암 치료제 FDA 승인 관련 기대감과 불확실성 혼재. 기관 수급은 긍정적이나 결과에 따른 변동성 예상.</t>
+          <t>HLB, 간암 신약 승인 기대감 속 기관 순매수. FDA 승인 관련 불확실성 상존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['간암 치료제', 'FDA 승인', '기관 수급']</t>
+          <t>['간암 신약', 'FDA 승인', '기관 순매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7190</v>
+        <v>7200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.18%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="H10" t="n">
         <v>25.47</v>
@@ -1346,7 +1346,7 @@
         <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>8577319815</v>
+        <v>8762083170</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>장기 적자 및 주가 하락세 지속, 실적 발표 후 폭락 및 최저가 수준 기록. 긍정적 전망은 희박.</t>
+          <t>LG디스플레이, 대규모 영업손실 발표 후 주가 급락 및 저점 논란. OLED 사업 경쟁 심화.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업손실', '주가 하락', '최저가']</t>
+          <t>['영업손실', '주가 급락', 'OLED']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,215 +1391,215 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215750</v>
+        <v>14540</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>473</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>1198</v>
+        <v>129</v>
       </c>
       <c r="H11" t="n">
-        <v>46.14</v>
+        <v>1.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>223500</v>
+        <v>14980</v>
       </c>
       <c r="K11" t="n">
-        <v>221500</v>
+        <v>14460</v>
       </c>
       <c r="L11" t="n">
-        <v>226000</v>
+        <v>16140</v>
       </c>
       <c r="M11" t="n">
-        <v>215000</v>
+        <v>13550</v>
       </c>
       <c r="N11" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1133910203500</v>
+        <v>71324568440</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>12030</v>
       </c>
       <c r="R11" t="n">
-        <v>-677000</v>
+        <v>-54000</v>
       </c>
       <c r="S11" t="n">
-        <v>-254000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 부정적인 증시 전망 관련 언급 다수. 외인 놀이터화 우려.</t>
+          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '증시 전망', '외인 투자']</t>
+          <t>['AI', '반도체', '수주잔고']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14460</v>
+        <v>216500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>482</v>
       </c>
       <c r="G12" t="n">
-        <v>128</v>
+        <v>1276</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>46.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14980</v>
+        <v>223500</v>
       </c>
       <c r="K12" t="n">
-        <v>14460</v>
+        <v>221500</v>
       </c>
       <c r="L12" t="n">
-        <v>16140</v>
+        <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>13550</v>
+        <v>215000</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>70921578220</v>
+        <v>1165812352250</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>12030</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-54000</v>
+        <v>-677000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-254000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
+          <t>정치적 요인에 따른 한국 증시 하락 전망 및 외국인 투자자 우려 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수주잔고']</t>
+          <t>['한국 증시', '외국인 투자자', '정치적 요인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1242000</v>
+        <v>9840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.02%</t>
+          <t>'-3.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>106</v>
       </c>
       <c r="F13" t="n">
-        <v>487</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>1847</v>
+        <v>294</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>5.87</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>10190</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>10110</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>10180</v>
       </c>
       <c r="M13" t="n">
-        <v>1240000</v>
+        <v>9620</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>5.34</v>
       </c>
       <c r="O13" t="n">
-        <v>1339472702500</v>
+        <v>13300463955</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>14940</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>5390</v>
       </c>
       <c r="R13" t="n">
-        <v>-55000</v>
+        <v>-32000</v>
       </c>
       <c r="S13" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 언급이 주를 이루며 반도체 산업 침체 우려.</t>
+          <t>테슬라 실적 발표 및 스페이스X 관련 뉴스에도 불구하고 주가 하락 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '반도체 산업', '증시 하락']</t>
+          <t>['테슬라', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9700</v>
+        <v>1247000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.81%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>496</v>
       </c>
       <c r="G14" t="n">
-        <v>297</v>
+        <v>1740</v>
       </c>
       <c r="H14" t="n">
-        <v>5.87</v>
+        <v>48.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10190</v>
+        <v>1294000</v>
       </c>
       <c r="K14" t="n">
-        <v>10110</v>
+        <v>1273000</v>
       </c>
       <c r="L14" t="n">
-        <v>10180</v>
+        <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>9700</v>
+        <v>1240000</v>
       </c>
       <c r="N14" t="n">
-        <v>5.34</v>
+        <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>12851685775</v>
+        <v>1372826393500</v>
       </c>
       <c r="P14" t="n">
-        <v>14940</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>5390</v>
+        <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-32000</v>
+        <v>-55000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 실적 호조와 스페이스X 관련 뉴스에도 불구하고 주가 하락 및 공매도 관련 우려.</t>
+          <t>정치적 이슈와 반도체 산업 부진에 따른 SK하이닉스 주가 하락 및 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['반도체 산업', '정치적 이슈', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10040</v>
+        <v>10070</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.87%</t>
+          <t>'-9.61%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15" t="n">
         <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>50917951535</v>
+        <v>51632418095</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 테마 속에서도 투자경고 및 투기예고로 인한 급락세.</t>
+          <t>HT로보틱스, 로봇주 테마 조정 및 ESS 마진율 불확실성으로 주가 급락. 투매 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투자경고', '급락']</t>
+          <t>['로봇주', 'ESS', '주가 급락']</t>
         </is>
       </c>
       <c r="X15" t="n">
